--- a/src/data/datasets/excel/loginData.xlsx
+++ b/src/data/datasets/excel/loginData.xlsx
@@ -415,7 +415,7 @@
         <v>web.validUser.email</v>
       </c>
       <c r="B2" t="str">
-        <v>anudeep.web@gmail.com</v>
+        <v>${webValidUserEmail}</v>
       </c>
       <c r="C2" t="str">
         <v>string</v>
@@ -426,7 +426,7 @@
         <v>web.validUser.password</v>
       </c>
       <c r="B3" t="str">
-        <v>Test@1234</v>
+        <v>${webValidUserPassword}</v>
       </c>
       <c r="C3" t="str">
         <v>string</v>
@@ -437,7 +437,7 @@
         <v>web.invalidPassword.email</v>
       </c>
       <c r="B4" t="str">
-        <v>anudeep.web@gmail.com</v>
+        <v>${webValidUserEmail}</v>
       </c>
       <c r="C4" t="str">
         <v>string</v>
@@ -481,7 +481,7 @@
         <v>api.validUser.email</v>
       </c>
       <c r="B8" t="str">
-        <v>anudeep.api@gmail.com</v>
+        <v>${apiValidUserEmail}</v>
       </c>
       <c r="C8" t="str">
         <v>string</v>
@@ -492,7 +492,7 @@
         <v>api.validUser.password</v>
       </c>
       <c r="B9" t="str">
-        <v>Test@1234</v>
+        <v>${apiValidUserPassword}</v>
       </c>
       <c r="C9" t="str">
         <v>string</v>

--- a/src/data/datasets/excel/loginData.xlsx
+++ b/src/data/datasets/excel/loginData.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -500,10 +500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>mobile.validUser.username</v>
+        <v>mobile.validUser.email</v>
       </c>
       <c r="B10" t="str">
-        <v>standard_user</v>
+        <v>${mobileValidUserEmail}</v>
       </c>
       <c r="C10" t="str">
         <v>string</v>
@@ -514,7 +514,7 @@
         <v>mobile.validUser.password</v>
       </c>
       <c r="B11" t="str">
-        <v>secret_sauce</v>
+        <v>${mobileValidUserPassword}</v>
       </c>
       <c r="C11" t="str">
         <v>string</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>mobile.invalidPassword.username</v>
+        <v>mobile.incorrectPassword.email</v>
       </c>
       <c r="B12" t="str">
-        <v>standard_user</v>
+        <v>${mobileValidUserEmail}</v>
       </c>
       <c r="C12" t="str">
         <v>string</v>
@@ -533,18 +533,62 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>mobile.invalidPassword.password</v>
+        <v>mobile.incorrectPassword.password</v>
       </c>
       <c r="B13" t="str">
-        <v>wrong_password</v>
+        <v>DefinitelyTheWrongPassword1!</v>
       </c>
       <c r="C13" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>mobile.blankCredentials.email</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>mobile.blankCredentials.password</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>mobile.malformedEmail.email</v>
+      </c>
+      <c r="B16" t="str">
+        <v>not-an-email</v>
+      </c>
+      <c r="C16" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>mobile.malformedEmail.password</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SomePassword1!</v>
+      </c>
+      <c r="C17" t="str">
         <v>string</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>